--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128675943</v>
+        <v>128675938</v>
       </c>
       <c r="B2" t="n">
-        <v>97457</v>
+        <v>57686</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>728851</v>
+        <v>728927</v>
       </c>
       <c r="R2" t="n">
-        <v>7112956</v>
+        <v>7113185</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128675938</v>
+        <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>57686</v>
+        <v>97463</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>728927</v>
+        <v>728851</v>
       </c>
       <c r="R3" t="n">
-        <v>7113185</v>
+        <v>7112956</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>96924</v>
+        <v>96930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>96924</v>
+        <v>96930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91423</v>
+        <v>91429</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -1160,27 +1160,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128675937</v>
+        <v>128675946</v>
       </c>
       <c r="B7" t="n">
-        <v>57686</v>
+        <v>58059</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>728937</v>
+        <v>728824</v>
       </c>
       <c r="R7" t="n">
-        <v>7113153</v>
+        <v>7112932</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,27 +1257,27 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128675946</v>
+        <v>128675937</v>
       </c>
       <c r="B8" t="n">
-        <v>58059</v>
+        <v>57686</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>728824</v>
+        <v>728937</v>
       </c>
       <c r="R8" t="n">
-        <v>7112932</v>
+        <v>7113153</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97463</v>
+        <v>97465</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128675949</v>
       </c>
       <c r="B4" t="n">
-        <v>75158</v>
+        <v>75160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128675952</v>
       </c>
       <c r="B5" t="n">
-        <v>75167</v>
+        <v>75169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128675951</v>
       </c>
       <c r="B6" t="n">
-        <v>82946</v>
+        <v>82948</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128675953</v>
       </c>
       <c r="B9" t="n">
-        <v>75167</v>
+        <v>75169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>96930</v>
+        <v>96932</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>96930</v>
+        <v>96932</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>128675950</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91429</v>
+        <v>91431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2916,6 +2916,2655 @@
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128766541</v>
+      </c>
+      <c r="B25" t="n">
+        <v>92163</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>729018</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7112948</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128766545</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>729070</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7112953</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128766562</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>728971</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7113048</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128766563</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>728978</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7113041</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128766548</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>729021</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7113049</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128766544</v>
+      </c>
+      <c r="B30" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>728746</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7112752</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128766566</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>728797</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7112801</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128766540</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>729028</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7113039</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128766546</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>728978</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7113062</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128766564</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79089</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>729047</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7113041</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128766547</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57686</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>729016</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7113057</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128766550</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97462</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>729083</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7112944</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128766555</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>729098</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7112944</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128766552</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97462</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>728757</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7112752</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128766549</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>728839</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7112834</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128766561</v>
+      </c>
+      <c r="B40" t="n">
+        <v>91484</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>728907</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7112919</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128766537</v>
+      </c>
+      <c r="B41" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>729030</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7113036</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128766558</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>728849</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7112937</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128766539</v>
+      </c>
+      <c r="B43" t="n">
+        <v>91466</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>729022</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7113057</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128766535</v>
+      </c>
+      <c r="B44" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>728755</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7112785</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128766542</v>
+      </c>
+      <c r="B45" t="n">
+        <v>92163</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>729022</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7113042</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128766536</v>
+      </c>
+      <c r="B46" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>729017</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7113049</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128766556</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>729099</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7112949</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128766538</v>
+      </c>
+      <c r="B48" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>728934</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7112948</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128766557</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>728939</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7112940</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128766560</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>728928</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7113054</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128766559</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>728867</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7113019</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Alva Danielsson, Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97465</v>
+        <v>97466</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>96932</v>
+        <v>96933</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>96932</v>
+        <v>96933</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>128766541</v>
       </c>
       <c r="B25" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>128766540</v>
       </c>
       <c r="B32" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>128766550</v>
       </c>
       <c r="B36" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128766555</v>
       </c>
       <c r="B37" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>128766552</v>
       </c>
       <c r="B38" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>128766549</v>
       </c>
       <c r="B39" t="n">
-        <v>91920</v>
+        <v>91921</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>128766561</v>
       </c>
       <c r="B40" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128766537</v>
       </c>
       <c r="B41" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>128766558</v>
       </c>
       <c r="B42" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>128766539</v>
       </c>
       <c r="B43" t="n">
-        <v>91466</v>
+        <v>91467</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128766535</v>
       </c>
       <c r="B44" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>128766542</v>
       </c>
       <c r="B45" t="n">
-        <v>92163</v>
+        <v>92164</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>128766536</v>
       </c>
       <c r="B46" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128766556</v>
       </c>
       <c r="B47" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128766538</v>
       </c>
       <c r="B48" t="n">
-        <v>91431</v>
+        <v>91432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>128766557</v>
       </c>
       <c r="B49" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>128766560</v>
       </c>
       <c r="B50" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>128766559</v>
       </c>
       <c r="B51" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128675938</v>
       </c>
       <c r="B2" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97466</v>
+        <v>97493</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128675949</v>
       </c>
       <c r="B4" t="n">
-        <v>75160</v>
+        <v>75187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128675952</v>
       </c>
       <c r="B5" t="n">
-        <v>75169</v>
+        <v>75196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128675951</v>
       </c>
       <c r="B6" t="n">
-        <v>82948</v>
+        <v>82975</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128675946</v>
       </c>
       <c r="B7" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128675937</v>
       </c>
       <c r="B8" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128675953</v>
       </c>
       <c r="B9" t="n">
-        <v>75169</v>
+        <v>75196</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128675939</v>
       </c>
       <c r="B10" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>96933</v>
+        <v>96960</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>96933</v>
+        <v>96960</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>128675940</v>
       </c>
       <c r="B15" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>128675942</v>
       </c>
       <c r="B17" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>128675945</v>
       </c>
       <c r="B19" t="n">
-        <v>58059</v>
+        <v>58086</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>128675950</v>
       </c>
       <c r="B20" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>128675941</v>
       </c>
       <c r="B21" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>128675936</v>
       </c>
       <c r="B23" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>128766541</v>
       </c>
       <c r="B25" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>128766545</v>
       </c>
       <c r="B26" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128766562</v>
       </c>
       <c r="B27" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128766563</v>
       </c>
       <c r="B28" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>128766548</v>
       </c>
       <c r="B29" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128766544</v>
       </c>
       <c r="B30" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>128766566</v>
       </c>
       <c r="B31" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>128766540</v>
       </c>
       <c r="B32" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>128766546</v>
       </c>
       <c r="B33" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>128766564</v>
       </c>
       <c r="B34" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>128766547</v>
       </c>
       <c r="B35" t="n">
-        <v>57686</v>
+        <v>57713</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>128766550</v>
       </c>
       <c r="B36" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128766555</v>
       </c>
       <c r="B37" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>128766552</v>
       </c>
       <c r="B38" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>128766549</v>
       </c>
       <c r="B39" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>128766561</v>
       </c>
       <c r="B40" t="n">
-        <v>91485</v>
+        <v>91512</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128766537</v>
       </c>
       <c r="B41" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>128766558</v>
       </c>
       <c r="B42" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>128766539</v>
       </c>
       <c r="B43" t="n">
-        <v>91467</v>
+        <v>91494</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128766535</v>
       </c>
       <c r="B44" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>128766542</v>
       </c>
       <c r="B45" t="n">
-        <v>92164</v>
+        <v>92191</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>128766536</v>
       </c>
       <c r="B46" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128766556</v>
       </c>
       <c r="B47" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128766538</v>
       </c>
       <c r="B48" t="n">
-        <v>91432</v>
+        <v>91459</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>128766557</v>
       </c>
       <c r="B49" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>128766560</v>
       </c>
       <c r="B50" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>128766559</v>
       </c>
       <c r="B51" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97493</v>
+        <v>97499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128675949</v>
       </c>
       <c r="B4" t="n">
-        <v>75187</v>
+        <v>75188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128675952</v>
       </c>
       <c r="B5" t="n">
-        <v>75196</v>
+        <v>75197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128675951</v>
       </c>
       <c r="B6" t="n">
-        <v>82975</v>
+        <v>82979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128675953</v>
       </c>
       <c r="B9" t="n">
-        <v>75196</v>
+        <v>75197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>96960</v>
+        <v>96966</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>96960</v>
+        <v>96966</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>128675950</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>128766541</v>
       </c>
       <c r="B25" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128766562</v>
       </c>
       <c r="B27" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128766563</v>
       </c>
       <c r="B28" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>128766566</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>128766540</v>
       </c>
       <c r="B32" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>128766564</v>
       </c>
       <c r="B34" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>128766550</v>
       </c>
       <c r="B36" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128766555</v>
       </c>
       <c r="B37" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>128766552</v>
       </c>
       <c r="B38" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>128766549</v>
       </c>
       <c r="B39" t="n">
-        <v>91948</v>
+        <v>91953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>128766561</v>
       </c>
       <c r="B40" t="n">
-        <v>91512</v>
+        <v>91517</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128766537</v>
       </c>
       <c r="B41" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>128766558</v>
       </c>
       <c r="B42" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>128766539</v>
       </c>
       <c r="B43" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128766535</v>
       </c>
       <c r="B44" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>128766542</v>
       </c>
       <c r="B45" t="n">
-        <v>92191</v>
+        <v>92196</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>128766536</v>
       </c>
       <c r="B46" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128766556</v>
       </c>
       <c r="B47" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128766538</v>
       </c>
       <c r="B48" t="n">
-        <v>91459</v>
+        <v>91464</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>128766557</v>
       </c>
       <c r="B49" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>128766560</v>
       </c>
       <c r="B50" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>128766559</v>
       </c>
       <c r="B51" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97499</v>
+        <v>97506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>96966</v>
+        <v>96973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>96966</v>
+        <v>96973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>128766541</v>
       </c>
       <c r="B25" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>128766540</v>
       </c>
       <c r="B32" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>128766550</v>
       </c>
       <c r="B36" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128766555</v>
       </c>
       <c r="B37" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>128766552</v>
       </c>
       <c r="B38" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>128766549</v>
       </c>
       <c r="B39" t="n">
-        <v>91953</v>
+        <v>91958</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>128766561</v>
       </c>
       <c r="B40" t="n">
-        <v>91517</v>
+        <v>91522</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128766537</v>
       </c>
       <c r="B41" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>128766558</v>
       </c>
       <c r="B42" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>128766539</v>
       </c>
       <c r="B43" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128766535</v>
       </c>
       <c r="B44" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>128766542</v>
       </c>
       <c r="B45" t="n">
-        <v>92196</v>
+        <v>92201</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>128766536</v>
       </c>
       <c r="B46" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128766556</v>
       </c>
       <c r="B47" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128766538</v>
       </c>
       <c r="B48" t="n">
-        <v>91464</v>
+        <v>91469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>128766557</v>
       </c>
       <c r="B49" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>128766560</v>
       </c>
       <c r="B50" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>128766559</v>
       </c>
       <c r="B51" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128675938</v>
       </c>
       <c r="B2" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97506</v>
+        <v>97510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128675949</v>
       </c>
       <c r="B4" t="n">
-        <v>75188</v>
+        <v>75192</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128675952</v>
       </c>
       <c r="B5" t="n">
-        <v>75197</v>
+        <v>75201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128675951</v>
       </c>
       <c r="B6" t="n">
-        <v>82979</v>
+        <v>82983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128675946</v>
       </c>
       <c r="B7" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128675937</v>
       </c>
       <c r="B8" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128675953</v>
       </c>
       <c r="B9" t="n">
-        <v>75197</v>
+        <v>75201</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128675939</v>
       </c>
       <c r="B10" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>96973</v>
+        <v>96977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>96973</v>
+        <v>96977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>128675940</v>
       </c>
       <c r="B15" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>128675942</v>
       </c>
       <c r="B17" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>128675945</v>
       </c>
       <c r="B19" t="n">
-        <v>58086</v>
+        <v>58090</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>128675950</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>128675941</v>
       </c>
       <c r="B21" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>128675936</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>128766541</v>
       </c>
       <c r="B25" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>128766545</v>
       </c>
       <c r="B26" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128766562</v>
       </c>
       <c r="B27" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128766563</v>
       </c>
       <c r="B28" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>128766548</v>
       </c>
       <c r="B29" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128766544</v>
       </c>
       <c r="B30" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>128766566</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>128766540</v>
       </c>
       <c r="B32" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>128766546</v>
       </c>
       <c r="B33" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>128766564</v>
       </c>
       <c r="B34" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>128766547</v>
       </c>
       <c r="B35" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>128766550</v>
       </c>
       <c r="B36" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128766555</v>
       </c>
       <c r="B37" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>128766552</v>
       </c>
       <c r="B38" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>128766549</v>
       </c>
       <c r="B39" t="n">
-        <v>91958</v>
+        <v>91962</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>128766561</v>
       </c>
       <c r="B40" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128766537</v>
       </c>
       <c r="B41" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>128766558</v>
       </c>
       <c r="B42" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>128766539</v>
       </c>
       <c r="B43" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128766535</v>
       </c>
       <c r="B44" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>128766542</v>
       </c>
       <c r="B45" t="n">
-        <v>92201</v>
+        <v>92205</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>128766536</v>
       </c>
       <c r="B46" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128766556</v>
       </c>
       <c r="B47" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128766538</v>
       </c>
       <c r="B48" t="n">
-        <v>91469</v>
+        <v>91473</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>128766557</v>
       </c>
       <c r="B49" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>128766560</v>
       </c>
       <c r="B50" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>128766559</v>
       </c>
       <c r="B51" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128675938</v>
       </c>
       <c r="B2" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97510</v>
+        <v>97517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128675949</v>
       </c>
       <c r="B4" t="n">
-        <v>75192</v>
+        <v>82988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128675952</v>
       </c>
       <c r="B5" t="n">
-        <v>75201</v>
+        <v>82997</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128675951</v>
       </c>
       <c r="B6" t="n">
-        <v>82983</v>
+        <v>82892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128675946</v>
       </c>
       <c r="B7" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128675937</v>
       </c>
       <c r="B8" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128675953</v>
       </c>
       <c r="B9" t="n">
-        <v>75201</v>
+        <v>82997</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128675939</v>
       </c>
       <c r="B10" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>96977</v>
+        <v>96984</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>96977</v>
+        <v>96984</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>128675940</v>
       </c>
       <c r="B15" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>128675942</v>
       </c>
       <c r="B17" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>128675945</v>
       </c>
       <c r="B19" t="n">
-        <v>58090</v>
+        <v>58093</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>128675950</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>128675941</v>
       </c>
       <c r="B21" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>128675936</v>
       </c>
       <c r="B23" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>128766541</v>
       </c>
       <c r="B25" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>128766545</v>
       </c>
       <c r="B26" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128766562</v>
       </c>
       <c r="B27" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128766563</v>
       </c>
       <c r="B28" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>128766548</v>
       </c>
       <c r="B29" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128766544</v>
       </c>
       <c r="B30" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>128766566</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>128766540</v>
       </c>
       <c r="B32" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>128766546</v>
       </c>
       <c r="B33" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>128766564</v>
       </c>
       <c r="B34" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>128766547</v>
       </c>
       <c r="B35" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>128766550</v>
       </c>
       <c r="B36" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128766555</v>
       </c>
       <c r="B37" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>128766552</v>
       </c>
       <c r="B38" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>128766549</v>
       </c>
       <c r="B39" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>128766561</v>
       </c>
       <c r="B40" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128766537</v>
       </c>
       <c r="B41" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>128766558</v>
       </c>
       <c r="B42" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>128766539</v>
       </c>
       <c r="B43" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128766535</v>
       </c>
       <c r="B44" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>128766542</v>
       </c>
       <c r="B45" t="n">
-        <v>92205</v>
+        <v>92210</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>128766536</v>
       </c>
       <c r="B46" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128766556</v>
       </c>
       <c r="B47" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128766538</v>
       </c>
       <c r="B48" t="n">
-        <v>91473</v>
+        <v>91478</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>128766557</v>
       </c>
       <c r="B49" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>128766560</v>
       </c>
       <c r="B50" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>128766559</v>
       </c>
       <c r="B51" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97525</v>
+        <v>97530</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>96992</v>
+        <v>96997</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>96992</v>
+        <v>96997</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>128766541</v>
       </c>
       <c r="B25" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>128766540</v>
       </c>
       <c r="B32" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>128766550</v>
       </c>
       <c r="B36" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128766555</v>
       </c>
       <c r="B37" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>128766552</v>
       </c>
       <c r="B38" t="n">
-        <v>97522</v>
+        <v>97527</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>128766549</v>
       </c>
       <c r="B39" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>128766561</v>
       </c>
       <c r="B40" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128766537</v>
       </c>
       <c r="B41" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>128766558</v>
       </c>
       <c r="B42" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>128766539</v>
       </c>
       <c r="B43" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128766535</v>
       </c>
       <c r="B44" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>128766542</v>
       </c>
       <c r="B45" t="n">
-        <v>92218</v>
+        <v>92223</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>128766536</v>
       </c>
       <c r="B46" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128766556</v>
       </c>
       <c r="B47" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128766538</v>
       </c>
       <c r="B48" t="n">
-        <v>91485</v>
+        <v>91488</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>128766557</v>
       </c>
       <c r="B49" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>128766560</v>
       </c>
       <c r="B50" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>128766559</v>
       </c>
       <c r="B51" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97530</v>
+        <v>97533</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128675949</v>
       </c>
       <c r="B4" t="n">
-        <v>82993</v>
+        <v>82994</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128675952</v>
       </c>
       <c r="B5" t="n">
-        <v>83002</v>
+        <v>83003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128675951</v>
       </c>
       <c r="B6" t="n">
-        <v>82897</v>
+        <v>82898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128675953</v>
       </c>
       <c r="B9" t="n">
-        <v>83002</v>
+        <v>83003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>96997</v>
+        <v>97000</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>96997</v>
+        <v>97000</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>128675950</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>128766541</v>
       </c>
       <c r="B25" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128766562</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128766563</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>128766566</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>128766540</v>
       </c>
       <c r="B32" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>128766564</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>128766550</v>
       </c>
       <c r="B36" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128766555</v>
       </c>
       <c r="B37" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>128766552</v>
       </c>
       <c r="B38" t="n">
-        <v>97527</v>
+        <v>97530</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>128766549</v>
       </c>
       <c r="B39" t="n">
-        <v>91978</v>
+        <v>91981</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>128766561</v>
       </c>
       <c r="B40" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128766537</v>
       </c>
       <c r="B41" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>128766558</v>
       </c>
       <c r="B42" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>128766539</v>
       </c>
       <c r="B43" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128766535</v>
       </c>
       <c r="B44" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>128766542</v>
       </c>
       <c r="B45" t="n">
-        <v>92223</v>
+        <v>92226</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>128766536</v>
       </c>
       <c r="B46" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128766556</v>
       </c>
       <c r="B47" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128766538</v>
       </c>
       <c r="B48" t="n">
-        <v>91488</v>
+        <v>91491</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>128766557</v>
       </c>
       <c r="B49" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>128766560</v>
       </c>
       <c r="B50" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>128766559</v>
       </c>
       <c r="B51" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128675938</v>
       </c>
       <c r="B2" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -765,7 +765,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97533</v>
+        <v>97543</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>128675949</v>
       </c>
       <c r="B4" t="n">
-        <v>82994</v>
+        <v>82998</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,7 +959,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>128675952</v>
       </c>
       <c r="B5" t="n">
-        <v>83003</v>
+        <v>83007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1066,7 +1066,7 @@
         <v>128675951</v>
       </c>
       <c r="B6" t="n">
-        <v>82898</v>
+        <v>82902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1163,7 +1163,7 @@
         <v>128675946</v>
       </c>
       <c r="B7" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1260,7 +1260,7 @@
         <v>128675937</v>
       </c>
       <c r="B8" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1357,7 +1357,7 @@
         <v>128675953</v>
       </c>
       <c r="B9" t="n">
-        <v>83003</v>
+        <v>83007</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1454,7 +1454,7 @@
         <v>128675939</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>97000</v>
+        <v>97010</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>97000</v>
+        <v>97010</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>128675940</v>
       </c>
       <c r="B15" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
         <v>128675942</v>
       </c>
       <c r="B17" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2339,7 +2339,7 @@
         <v>128675945</v>
       </c>
       <c r="B19" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2436,7 +2436,7 @@
         <v>128675950</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2533,7 +2533,7 @@
         <v>128675941</v>
       </c>
       <c r="B21" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2727,7 +2727,7 @@
         <v>128675936</v>
       </c>
       <c r="B23" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -2921,7 +2921,7 @@
         <v>128766541</v>
       </c>
       <c r="B25" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>128766545</v>
       </c>
       <c r="B26" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128766562</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128766563</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>128766548</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128766544</v>
       </c>
       <c r="B30" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>128766566</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>128766540</v>
       </c>
       <c r="B32" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>128766546</v>
       </c>
       <c r="B33" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>128766564</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>128766547</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>128766550</v>
       </c>
       <c r="B36" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128766555</v>
       </c>
       <c r="B37" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>128766552</v>
       </c>
       <c r="B38" t="n">
-        <v>97530</v>
+        <v>97540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>128766549</v>
       </c>
       <c r="B39" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>128766561</v>
       </c>
       <c r="B40" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128766537</v>
       </c>
       <c r="B41" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>128766558</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>128766539</v>
       </c>
       <c r="B43" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128766535</v>
       </c>
       <c r="B44" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>128766542</v>
       </c>
       <c r="B45" t="n">
-        <v>92226</v>
+        <v>92233</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>128766536</v>
       </c>
       <c r="B46" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128766556</v>
       </c>
       <c r="B47" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128766538</v>
       </c>
       <c r="B48" t="n">
-        <v>91491</v>
+        <v>91497</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>128766557</v>
       </c>
       <c r="B49" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>128766560</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>128766559</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97543</v>
+        <v>97550</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128675949</v>
       </c>
       <c r="B4" t="n">
-        <v>82998</v>
+        <v>82988</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128675952</v>
       </c>
       <c r="B5" t="n">
-        <v>83007</v>
+        <v>82997</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128675951</v>
       </c>
       <c r="B6" t="n">
-        <v>82902</v>
+        <v>82871</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128675953</v>
       </c>
       <c r="B9" t="n">
-        <v>83007</v>
+        <v>82997</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>97010</v>
+        <v>97017</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>97010</v>
+        <v>97017</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>128766541</v>
       </c>
       <c r="B25" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>128766540</v>
       </c>
       <c r="B32" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>128766550</v>
       </c>
       <c r="B36" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128766555</v>
       </c>
       <c r="B37" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>128766552</v>
       </c>
       <c r="B38" t="n">
-        <v>97540</v>
+        <v>97547</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>128766549</v>
       </c>
       <c r="B39" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>128766561</v>
       </c>
       <c r="B40" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128766537</v>
       </c>
       <c r="B41" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>128766558</v>
       </c>
       <c r="B42" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>128766539</v>
       </c>
       <c r="B43" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128766535</v>
       </c>
       <c r="B44" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>128766542</v>
       </c>
       <c r="B45" t="n">
-        <v>92233</v>
+        <v>92240</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>128766536</v>
       </c>
       <c r="B46" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128766556</v>
       </c>
       <c r="B47" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128766538</v>
       </c>
       <c r="B48" t="n">
-        <v>91497</v>
+        <v>91504</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>128766557</v>
       </c>
       <c r="B49" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>128766560</v>
       </c>
       <c r="B50" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>128766559</v>
       </c>
       <c r="B51" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128675938</v>
       </c>
       <c r="B2" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97550</v>
+        <v>97552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128675949</v>
       </c>
       <c r="B4" t="n">
-        <v>82988</v>
+        <v>82990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128675952</v>
       </c>
       <c r="B5" t="n">
-        <v>82997</v>
+        <v>82999</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128675951</v>
       </c>
       <c r="B6" t="n">
-        <v>82871</v>
+        <v>82873</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>128675946</v>
       </c>
       <c r="B7" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>128675937</v>
       </c>
       <c r="B8" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128675953</v>
       </c>
       <c r="B9" t="n">
-        <v>82997</v>
+        <v>82999</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>128675939</v>
       </c>
       <c r="B10" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>97017</v>
+        <v>97019</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>97017</v>
+        <v>97019</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>128675940</v>
       </c>
       <c r="B15" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>128675942</v>
       </c>
       <c r="B17" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>128675945</v>
       </c>
       <c r="B19" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>128675950</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2533,7 +2533,7 @@
         <v>128675941</v>
       </c>
       <c r="B21" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2727,7 +2727,7 @@
         <v>128675936</v>
       </c>
       <c r="B23" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>128766541</v>
       </c>
       <c r="B25" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
         <v>128766545</v>
       </c>
       <c r="B26" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>128766562</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>128766563</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3309,7 +3309,7 @@
         <v>128766548</v>
       </c>
       <c r="B29" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>128766544</v>
       </c>
       <c r="B30" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>128766566</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>128766540</v>
       </c>
       <c r="B32" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         <v>128766546</v>
       </c>
       <c r="B33" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>128766564</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,7 +3891,7 @@
         <v>128766547</v>
       </c>
       <c r="B35" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,7 +3988,7 @@
         <v>128766550</v>
       </c>
       <c r="B36" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         <v>128766555</v>
       </c>
       <c r="B37" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>128766552</v>
       </c>
       <c r="B38" t="n">
-        <v>97547</v>
+        <v>97549</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>128766549</v>
       </c>
       <c r="B39" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>128766561</v>
       </c>
       <c r="B40" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>128766537</v>
       </c>
       <c r="B41" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>128766558</v>
       </c>
       <c r="B42" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>128766539</v>
       </c>
       <c r="B43" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>128766535</v>
       </c>
       <c r="B44" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4871,7 +4871,7 @@
         <v>128766542</v>
       </c>
       <c r="B45" t="n">
-        <v>92240</v>
+        <v>92242</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4968,7 +4968,7 @@
         <v>128766536</v>
       </c>
       <c r="B46" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>128766556</v>
       </c>
       <c r="B47" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         <v>128766538</v>
       </c>
       <c r="B48" t="n">
-        <v>91504</v>
+        <v>91506</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5264,7 +5264,7 @@
         <v>128766557</v>
       </c>
       <c r="B49" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5366,7 +5366,7 @@
         <v>128766560</v>
       </c>
       <c r="B50" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>128766559</v>
       </c>
       <c r="B51" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97552</v>
+        <v>97578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>97019</v>
+        <v>97045</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>97019</v>
+        <v>97045</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91506</v>
+        <v>91504</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>97045</v>
+        <v>97046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>97045</v>
+        <v>97046</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97579</v>
+        <v>97580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>97046</v>
+        <v>97047</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>97046</v>
+        <v>97047</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97580</v>
+        <v>97584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128675949</v>
       </c>
       <c r="B4" t="n">
-        <v>82990</v>
+        <v>82994</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128675952</v>
       </c>
       <c r="B5" t="n">
-        <v>82999</v>
+        <v>83003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128675951</v>
       </c>
       <c r="B6" t="n">
-        <v>82873</v>
+        <v>82877</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128675953</v>
       </c>
       <c r="B9" t="n">
-        <v>82999</v>
+        <v>83003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>97047</v>
+        <v>97051</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>97047</v>
+        <v>97051</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>128675950</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91504</v>
+        <v>91507</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97584</v>
+        <v>97586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128675949</v>
       </c>
       <c r="B4" t="n">
-        <v>82994</v>
+        <v>82995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>128675952</v>
       </c>
       <c r="B5" t="n">
-        <v>83003</v>
+        <v>83004</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>128675951</v>
       </c>
       <c r="B6" t="n">
-        <v>82877</v>
+        <v>82878</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>128675953</v>
       </c>
       <c r="B9" t="n">
-        <v>83003</v>
+        <v>83004</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>97051</v>
+        <v>97053</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>97051</v>
+        <v>97053</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>128675950</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91507</v>
+        <v>91509</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97586</v>
+        <v>97590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>97053</v>
+        <v>97057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>97053</v>
+        <v>97057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91509</v>
+        <v>91513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128675943</v>
       </c>
       <c r="B3" t="n">
-        <v>97590</v>
+        <v>97598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>128675947</v>
       </c>
       <c r="B11" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>128675932</v>
       </c>
       <c r="B12" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>128675933</v>
       </c>
       <c r="B13" t="n">
-        <v>97057</v>
+        <v>97065</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>128675934</v>
       </c>
       <c r="B14" t="n">
-        <v>97057</v>
+        <v>97065</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>128675929</v>
       </c>
       <c r="B16" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>128675948</v>
       </c>
       <c r="B18" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2630,7 +2630,7 @@
         <v>128675931</v>
       </c>
       <c r="B22" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>128675930</v>
       </c>
       <c r="B24" t="n">
-        <v>91513</v>
+        <v>91514</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128675938</v>
+        <v>128766544</v>
       </c>
       <c r="B2" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>728927</v>
+        <v>728746</v>
       </c>
       <c r="R2" t="n">
-        <v>7113185</v>
+        <v>7112752</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128675943</v>
+        <v>128675952</v>
       </c>
       <c r="B3" t="n">
-        <v>97598</v>
+        <v>83299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221946</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>728851</v>
+        <v>728880</v>
       </c>
       <c r="R3" t="n">
-        <v>7112956</v>
+        <v>7113048</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128675949</v>
+        <v>128675953</v>
       </c>
       <c r="B4" t="n">
-        <v>82995</v>
+        <v>83299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6439</v>
+        <v>308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128675952</v>
+        <v>128766539</v>
       </c>
       <c r="B5" t="n">
-        <v>83004</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>728880</v>
+        <v>729022</v>
       </c>
       <c r="R5" t="n">
-        <v>7113048</v>
+        <v>7113057</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128675951</v>
+        <v>128766540</v>
       </c>
       <c r="B6" t="n">
-        <v>82878</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>728838</v>
+        <v>729028</v>
       </c>
       <c r="R6" t="n">
-        <v>7112918</v>
+        <v>7113039</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,44 +1148,44 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128675946</v>
+        <v>128766549</v>
       </c>
       <c r="B7" t="n">
-        <v>58097</v>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>728824</v>
+        <v>728839</v>
       </c>
       <c r="R7" t="n">
-        <v>7112932</v>
+        <v>7112834</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128675937</v>
+        <v>128675951</v>
       </c>
       <c r="B8" t="n">
-        <v>57724</v>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>728937</v>
+        <v>728838</v>
       </c>
       <c r="R8" t="n">
-        <v>7113153</v>
+        <v>7112918</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128675953</v>
+        <v>128675933</v>
       </c>
       <c r="B9" t="n">
-        <v>83004</v>
+        <v>97453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>1841</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>728859</v>
+        <v>728943</v>
       </c>
       <c r="R9" t="n">
-        <v>7112990</v>
+        <v>7113153</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128675939</v>
+        <v>128675934</v>
       </c>
       <c r="B10" t="n">
-        <v>57724</v>
+        <v>97453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1841</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>728871</v>
+        <v>728824</v>
       </c>
       <c r="R10" t="n">
-        <v>7113114</v>
+        <v>7112932</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128675947</v>
+        <v>128766541</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>92632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>3298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>728874</v>
+        <v>729018</v>
       </c>
       <c r="R11" t="n">
-        <v>7113016</v>
+        <v>7112948</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1621,40 +1621,34 @@
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 100 st</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128675932</v>
+        <v>128766542</v>
       </c>
       <c r="B12" t="n">
-        <v>91514</v>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>728780</v>
+        <v>729022</v>
       </c>
       <c r="R12" t="n">
-        <v>7112785</v>
+        <v>7113042</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1736,44 +1730,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128675933</v>
+        <v>128675929</v>
       </c>
       <c r="B13" t="n">
-        <v>97065</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1841</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1783,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>728943</v>
+        <v>728868</v>
       </c>
       <c r="R13" t="n">
-        <v>7113153</v>
+        <v>7112931</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128675934</v>
+        <v>128675930</v>
       </c>
       <c r="B14" t="n">
-        <v>97065</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1841</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflikmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lophozia guttulata</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Lindb. &amp; Arnell) A.Evans</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>728824</v>
+        <v>728943</v>
       </c>
       <c r="R14" t="n">
-        <v>7112932</v>
+        <v>7113153</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1942,32 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128675940</v>
+        <v>128675931</v>
       </c>
       <c r="B15" t="n">
-        <v>57724</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1977,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>728852</v>
+        <v>728930</v>
       </c>
       <c r="R15" t="n">
-        <v>7113029</v>
+        <v>7113150</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2039,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128675929</v>
+        <v>128675932</v>
       </c>
       <c r="B16" t="n">
-        <v>91514</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>728868</v>
+        <v>728780</v>
       </c>
       <c r="R16" t="n">
-        <v>7112931</v>
+        <v>7112785</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2136,32 +2130,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128675942</v>
+        <v>128766535</v>
       </c>
       <c r="B17" t="n">
-        <v>57724</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2171,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>728812</v>
+        <v>728755</v>
       </c>
       <c r="R17" t="n">
-        <v>7112892</v>
+        <v>7112785</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2221,44 +2215,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128675948</v>
+        <v>128766536</v>
       </c>
       <c r="B18" t="n">
-        <v>98724</v>
+        <v>91872</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>728921</v>
+        <v>729017</v>
       </c>
       <c r="R18" t="n">
-        <v>7113061</v>
+        <v>7113049</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2306,40 +2300,34 @@
           <t>2025-09-23</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 10 st</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128675945</v>
+        <v>128766537</v>
       </c>
       <c r="B19" t="n">
-        <v>58097</v>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2347,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2371,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>728921</v>
+        <v>729030</v>
       </c>
       <c r="R19" t="n">
-        <v>7113154</v>
+        <v>7113036</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,44 +2409,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128675950</v>
+        <v>128766538</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2468,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>728798</v>
+        <v>728934</v>
       </c>
       <c r="R20" t="n">
-        <v>7112828</v>
+        <v>7112948</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2518,44 +2506,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128675941</v>
+        <v>128675950</v>
       </c>
       <c r="B21" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2565,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>728828</v>
+        <v>728798</v>
       </c>
       <c r="R21" t="n">
-        <v>7112922</v>
+        <v>7112828</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2627,32 +2615,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128675931</v>
+        <v>128766562</v>
       </c>
       <c r="B22" t="n">
-        <v>91514</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2662,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>728930</v>
+        <v>728971</v>
       </c>
       <c r="R22" t="n">
-        <v>7113150</v>
+        <v>7113048</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2712,44 +2700,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128675936</v>
+        <v>128766563</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2762,7 +2750,7 @@
         <v>728978</v>
       </c>
       <c r="R23" t="n">
-        <v>7113110</v>
+        <v>7113041</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2809,44 +2797,44 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128675930</v>
+        <v>128766564</v>
       </c>
       <c r="B24" t="n">
-        <v>91514</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2856,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>728943</v>
+        <v>729047</v>
       </c>
       <c r="R24" t="n">
-        <v>7113153</v>
+        <v>7113041</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2906,44 +2894,44 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Alva Danielsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Elin Kannerby, Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128766541</v>
+        <v>128766565</v>
       </c>
       <c r="B25" t="n">
-        <v>92242</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2953,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>729018</v>
+        <v>728868</v>
       </c>
       <c r="R25" t="n">
-        <v>7112948</v>
+        <v>7112868</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3008,39 +2996,39 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128766545</v>
+        <v>128766566</v>
       </c>
       <c r="B26" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3050,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>729070</v>
+        <v>728797</v>
       </c>
       <c r="R26" t="n">
-        <v>7112953</v>
+        <v>7112801</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3112,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128766562</v>
+        <v>128675949</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>83290</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3147,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>728971</v>
+        <v>728859</v>
       </c>
       <c r="R27" t="n">
-        <v>7113048</v>
+        <v>7112990</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3197,44 +3185,44 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128766563</v>
+        <v>128675936</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3247,7 +3235,7 @@
         <v>728978</v>
       </c>
       <c r="R28" t="n">
-        <v>7113041</v>
+        <v>7113110</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3294,26 +3282,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128766548</v>
+        <v>128675937</v>
       </c>
       <c r="B29" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3341,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>729021</v>
+        <v>728937</v>
       </c>
       <c r="R29" t="n">
-        <v>7113049</v>
+        <v>7113153</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3391,26 +3379,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128766544</v>
+        <v>128675938</v>
       </c>
       <c r="B30" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3438,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>728746</v>
+        <v>728927</v>
       </c>
       <c r="R30" t="n">
-        <v>7112752</v>
+        <v>7113185</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3488,44 +3476,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128766566</v>
+        <v>128675939</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>57950</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3535,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>728797</v>
+        <v>728871</v>
       </c>
       <c r="R31" t="n">
-        <v>7112801</v>
+        <v>7113114</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3585,44 +3573,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128766540</v>
+        <v>128675940</v>
       </c>
       <c r="B32" t="n">
-        <v>91542</v>
+        <v>57950</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3632,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>729028</v>
+        <v>728852</v>
       </c>
       <c r="R32" t="n">
-        <v>7113039</v>
+        <v>7113029</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3682,26 +3670,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128766546</v>
+        <v>128675941</v>
       </c>
       <c r="B33" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3729,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>728978</v>
+        <v>728828</v>
       </c>
       <c r="R33" t="n">
-        <v>7113062</v>
+        <v>7112922</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3779,44 +3767,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128766564</v>
+        <v>128675942</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>57950</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3826,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>729047</v>
+        <v>728812</v>
       </c>
       <c r="R34" t="n">
-        <v>7113041</v>
+        <v>7112892</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3876,26 +3864,26 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128766547</v>
+        <v>128766545</v>
       </c>
       <c r="B35" t="n">
-        <v>57724</v>
+        <v>57950</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -3923,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>729016</v>
+        <v>729070</v>
       </c>
       <c r="R35" t="n">
-        <v>7113057</v>
+        <v>7112953</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3985,10 +3973,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128766550</v>
+        <v>128766546</v>
       </c>
       <c r="B36" t="n">
-        <v>97549</v>
+        <v>57950</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3996,21 +3984,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4020,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>729083</v>
+        <v>728978</v>
       </c>
       <c r="R36" t="n">
-        <v>7112944</v>
+        <v>7113062</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4082,49 +4070,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128766555</v>
+        <v>128766547</v>
       </c>
       <c r="B37" t="n">
-        <v>98678</v>
+        <v>57950</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Eriksdal, Vb</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>729098</v>
+        <v>729016</v>
       </c>
       <c r="R37" t="n">
-        <v>7112944</v>
+        <v>7113057</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4165,7 +4149,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4184,10 +4167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128766552</v>
+        <v>128766548</v>
       </c>
       <c r="B38" t="n">
-        <v>97549</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4195,21 +4178,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4219,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>728757</v>
+        <v>729021</v>
       </c>
       <c r="R38" t="n">
-        <v>7112752</v>
+        <v>7113049</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4281,32 +4264,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128766549</v>
+        <v>128675945</v>
       </c>
       <c r="B39" t="n">
-        <v>91997</v>
+        <v>58327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>103015</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>728839</v>
+        <v>728921</v>
       </c>
       <c r="R39" t="n">
-        <v>7112834</v>
+        <v>7113154</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,44 +4349,44 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128766561</v>
+        <v>128675946</v>
       </c>
       <c r="B40" t="n">
-        <v>91560</v>
+        <v>58327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>103015</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4396,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>728907</v>
+        <v>728824</v>
       </c>
       <c r="R40" t="n">
-        <v>7112919</v>
+        <v>7112932</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,44 +4446,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128766537</v>
+        <v>128766543</v>
       </c>
       <c r="B41" t="n">
-        <v>91506</v>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4510,10 +4493,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>729030</v>
+        <v>728777</v>
       </c>
       <c r="R41" t="n">
-        <v>7113036</v>
+        <v>7112762</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,17 +4548,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128766558</v>
+        <v>128675947</v>
       </c>
       <c r="B42" t="n">
-        <v>98678</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4600,21 +4583,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Eriksdal, Vb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>728849</v>
+        <v>728874</v>
       </c>
       <c r="R42" t="n">
-        <v>7112937</v>
+        <v>7113016</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4649,6 +4628,11 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ca 100 st</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -4662,44 +4646,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Elin Kannerby</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128766539</v>
+        <v>128675948</v>
       </c>
       <c r="B43" t="n">
-        <v>91542</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4709,10 +4693,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>729022</v>
+        <v>728921</v>
       </c>
       <c r="R43" t="n">
-        <v>7113057</v>
+        <v>7113061</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4747,69 +4731,79 @@
           <t>2025-09-23</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ca 10 st</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Elin Kannerby, Alva Danielsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128766535</v>
+        <v>128766555</v>
       </c>
       <c r="B44" t="n">
-        <v>91506</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Eriksdal, Vb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>728755</v>
+        <v>729098</v>
       </c>
       <c r="R44" t="n">
-        <v>7112785</v>
+        <v>7112944</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4850,6 +4844,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -4861,52 +4856,56 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128766542</v>
+        <v>128766556</v>
       </c>
       <c r="B45" t="n">
-        <v>92242</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3298</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Eriksdal, Vb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>729022</v>
+        <v>729099</v>
       </c>
       <c r="R45" t="n">
-        <v>7113042</v>
+        <v>7112949</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4947,6 +4946,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -4965,45 +4965,49 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128766536</v>
+        <v>128766557</v>
       </c>
       <c r="B46" t="n">
-        <v>91506</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Eriksdal, Vb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>729017</v>
+        <v>728939</v>
       </c>
       <c r="R46" t="n">
-        <v>7113049</v>
+        <v>7112940</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5044,6 +5048,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5055,17 +5060,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128766556</v>
+        <v>128766558</v>
       </c>
       <c r="B47" t="n">
-        <v>98678</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5092,7 +5097,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5101,10 +5106,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>729099</v>
+        <v>728849</v>
       </c>
       <c r="R47" t="n">
-        <v>7112949</v>
+        <v>7112937</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5164,45 +5169,49 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128766538</v>
+        <v>128766559</v>
       </c>
       <c r="B48" t="n">
-        <v>91506</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Eriksdal, Vb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>728934</v>
+        <v>728867</v>
       </c>
       <c r="R48" t="n">
-        <v>7112948</v>
+        <v>7113019</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5243,6 +5252,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5254,17 +5264,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Alva Danielsson</t>
+          <t>Alva Danielsson, Elin Kannerby</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128766557</v>
+        <v>128766560</v>
       </c>
       <c r="B49" t="n">
-        <v>98678</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5291,7 +5301,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -5300,10 +5310,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>728939</v>
+        <v>728928</v>
       </c>
       <c r="R49" t="n">
-        <v>7112940</v>
+        <v>7113054</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5363,49 +5373,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128766560</v>
+        <v>128766550</v>
       </c>
       <c r="B50" t="n">
-        <v>98678</v>
+        <v>97983</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Eriksdal, Vb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>728928</v>
+        <v>729083</v>
       </c>
       <c r="R50" t="n">
-        <v>7113054</v>
+        <v>7112944</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5446,7 +5452,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5465,49 +5470,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128766559</v>
+        <v>128766552</v>
       </c>
       <c r="B51" t="n">
-        <v>98678</v>
+        <v>97983</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Eriksdal, Vb</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>728867</v>
+        <v>728757</v>
       </c>
       <c r="R51" t="n">
-        <v>7113019</v>
+        <v>7112752</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5548,7 +5549,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5564,6 +5564,103 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128675943</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Eriksdal, Vb</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>728851</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7112956</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-09-23</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Elin Kannerby, Alva Danielsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39786-2025 artfynd.xlsx
+++ b/artfynd/A 39786-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AZ52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675952</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675953</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766539</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766540</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766549</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675951</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675933</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675934</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766541</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766542</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675929</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675930</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675931</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675932</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766535</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766536</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766537</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766538</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675950</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766562</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766563</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766564</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766565</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766566</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675949</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675936</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675937</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675938</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675939</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675940</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675941</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675942</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766544</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766545</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766546</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766547</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766548</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675945</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675946</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766543</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4655,6 +4860,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675947</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4758,6 +4968,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675948</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4860,6 +5075,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766555</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4962,6 +5182,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766556</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5064,6 +5289,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766557</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5166,6 +5396,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766558</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5268,6 +5503,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766559</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5370,6 +5610,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766560</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5467,6 +5712,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766550</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5564,6 +5814,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128766552</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5661,8 +5916,66 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128675943</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>